--- a/branches/fix/go-publish-fhir-settings/StructureDefinition-mii-ex-bildgebung-gewicht.xlsx
+++ b/branches/fix/go-publish-fhir-settings/StructureDefinition-mii-ex-bildgebung-gewicht.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T16:30:45+00:00</t>
+    <t>2026-09-14T16:59:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/fix/go-publish-fhir-settings/StructureDefinition-mii-ex-bildgebung-gewicht.xlsx
+++ b/branches/fix/go-publish-fhir-settings/StructureDefinition-mii-ex-bildgebung-gewicht.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T16:59:03+00:00</t>
+    <t>2026-09-14T17:22:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
